--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="735">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -756,6 +756,24 @@
     <t>Polyneuropati UNS</t>
   </si>
   <si>
+    <t>DG83</t>
+  </si>
+  <si>
+    <t>Andre syndromer med lammelse</t>
+  </si>
+  <si>
+    <t>DG834</t>
+  </si>
+  <si>
+    <t>Cauda equina-syndrom</t>
+  </si>
+  <si>
+    <t>DG834B</t>
+  </si>
+  <si>
+    <t>Neurogen claudicatio intermittens</t>
+  </si>
+  <si>
     <t>DI20</t>
   </si>
   <si>
@@ -906,12 +924,60 @@
     <t>Kronisk iskæmisk hjertesygdom UNS</t>
   </si>
   <si>
+    <t>DI34</t>
+  </si>
+  <si>
+    <t>Ikke-reumatiske sygdomme i mitralklappen</t>
+  </si>
+  <si>
+    <t>DI340</t>
+  </si>
+  <si>
+    <t>Mitralinsufficiens</t>
+  </si>
+  <si>
+    <t>DI35</t>
+  </si>
+  <si>
+    <t>Ikke-reumatiske sygdomme i aortaklappen</t>
+  </si>
+  <si>
+    <t>DI350</t>
+  </si>
+  <si>
+    <t>Aortastenose</t>
+  </si>
+  <si>
+    <t>DI48</t>
+  </si>
+  <si>
+    <t>Atrieflagren og atrieflimren</t>
+  </si>
+  <si>
     <t>DI50</t>
   </si>
   <si>
     <t>Hjertesvigt</t>
   </si>
   <si>
+    <t>DI51</t>
+  </si>
+  <si>
+    <t>Dårligt definerede hjertesygdomme og komplikationer til hjertesygdomme</t>
+  </si>
+  <si>
+    <t>DI511</t>
+  </si>
+  <si>
+    <t>Ruptur af chordae tendineae IKA</t>
+  </si>
+  <si>
+    <t>DI511A</t>
+  </si>
+  <si>
+    <t>Mitralklapinsufficiens ved chordaruptur</t>
+  </si>
+  <si>
     <t>DI70</t>
   </si>
   <si>
@@ -936,6 +1002,42 @@
     <t>Aterosklerose i anden arterie</t>
   </si>
   <si>
+    <t>DI71</t>
+  </si>
+  <si>
+    <t>Aorta-aneurisme og aortadissektion</t>
+  </si>
+  <si>
+    <t>DI719</t>
+  </si>
+  <si>
+    <t>Aorta-aneurisme UNS uden ruptur</t>
+  </si>
+  <si>
+    <t>DI719A</t>
+  </si>
+  <si>
+    <t>Dilateret aorta</t>
+  </si>
+  <si>
+    <t>DI73</t>
+  </si>
+  <si>
+    <t>Andre sygdomme i perifere kar</t>
+  </si>
+  <si>
+    <t>DI739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sygdom i perifere kar UNS </t>
+  </si>
+  <si>
+    <t>DI739A</t>
+  </si>
+  <si>
+    <t>Claudicatio intermittens</t>
+  </si>
+  <si>
     <t>DI83</t>
   </si>
   <si>
@@ -1044,6 +1146,12 @@
     <t>Kronisk obstruktiv lungesygdom UNS</t>
   </si>
   <si>
+    <t>DJ45</t>
+  </si>
+  <si>
+    <t>Astma</t>
+  </si>
+  <si>
     <t>DL02</t>
   </si>
   <si>
@@ -1446,6 +1554,24 @@
     <t>Neuropatisk artropati</t>
   </si>
   <si>
+    <t>DM16</t>
+  </si>
+  <si>
+    <t>Slidgigt i hofte</t>
+  </si>
+  <si>
+    <t>DM17</t>
+  </si>
+  <si>
+    <t>Slidgigt i knæ</t>
+  </si>
+  <si>
+    <t>DM54</t>
+  </si>
+  <si>
+    <t>Rygsmerter</t>
+  </si>
+  <si>
     <t>DM72</t>
   </si>
   <si>
@@ -1458,6 +1584,36 @@
     <t>Nekrotiserende bløddelsinfektion</t>
   </si>
   <si>
+    <t>DQ23</t>
+  </si>
+  <si>
+    <t>Medfødte misdannelser af aorta- og mitralklapperne</t>
+  </si>
+  <si>
+    <t>DQ231</t>
+  </si>
+  <si>
+    <t>Medfødt aortaklapinsufficiens</t>
+  </si>
+  <si>
+    <t>DQ231A</t>
+  </si>
+  <si>
+    <t>Valvula aortae bicuspidalis</t>
+  </si>
+  <si>
+    <t>DQ25</t>
+  </si>
+  <si>
+    <t>Medfødte misdannelser i de store arterier</t>
+  </si>
+  <si>
+    <t>DQ251</t>
+  </si>
+  <si>
+    <t>Coarctatio aortae</t>
+  </si>
+  <si>
     <t>DQ82</t>
   </si>
   <si>
@@ -2008,6 +2164,18 @@
   </si>
   <si>
     <t>Hudtransplanteret</t>
+  </si>
+  <si>
+    <t>DZ95</t>
+  </si>
+  <si>
+    <t>Tilstand med hjerte- eller karimplantater og -transplantater</t>
+  </si>
+  <si>
+    <t>DZ952</t>
+  </si>
+  <si>
+    <t>Tilstand med kunstig hjerteklap</t>
   </si>
   <si>
     <t>ZZ0150</t>
@@ -2363,7 +2531,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3630,7 +3798,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>253</v>
@@ -3654,7 +3822,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>257</v>
@@ -3678,7 +3846,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>261</v>
@@ -3690,7 +3858,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>263</v>
@@ -3702,7 +3870,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>265</v>
@@ -3714,7 +3882,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>267</v>
@@ -3726,7 +3894,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>269</v>
@@ -3738,7 +3906,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>271</v>
@@ -3762,7 +3930,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>275</v>
@@ -3774,7 +3942,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>277</v>
@@ -3786,7 +3954,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>279</v>
@@ -3798,7 +3966,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>281</v>
@@ -3810,7 +3978,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>283</v>
@@ -3834,7 +4002,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>287</v>
@@ -3858,7 +4026,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>291</v>
@@ -3870,7 +4038,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>293</v>
@@ -3894,7 +4062,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>297</v>
@@ -3906,7 +4074,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>299</v>
@@ -3930,7 +4098,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>303</v>
@@ -3978,7 +4146,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>311</v>
@@ -3990,7 +4158,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>313</v>
@@ -4002,7 +4170,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>315</v>
@@ -4026,7 +4194,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>319</v>
@@ -4038,7 +4206,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>321</v>
@@ -4050,7 +4218,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>323</v>
@@ -4062,7 +4230,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>325</v>
@@ -4074,7 +4242,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>327</v>
@@ -4086,7 +4254,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>329</v>
@@ -4110,7 +4278,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>333</v>
@@ -4122,7 +4290,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>335</v>
@@ -4134,7 +4302,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>337</v>
@@ -4158,7 +4326,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>341</v>
@@ -4170,7 +4338,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>343</v>
@@ -4182,7 +4350,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>345</v>
@@ -4254,7 +4422,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>357</v>
@@ -4314,7 +4482,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>367</v>
@@ -4326,7 +4494,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>369</v>
@@ -4338,7 +4506,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>371</v>
@@ -4350,7 +4518,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>373</v>
@@ -4362,7 +4530,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>375</v>
@@ -4374,7 +4542,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>377</v>
@@ -4386,7 +4554,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>379</v>
@@ -4398,7 +4566,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>381</v>
@@ -4410,7 +4578,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>383</v>
@@ -4422,7 +4590,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>385</v>
@@ -4458,7 +4626,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>391</v>
@@ -4470,7 +4638,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>393</v>
@@ -4482,7 +4650,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>395</v>
@@ -4494,7 +4662,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>397</v>
@@ -4518,7 +4686,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>401</v>
@@ -4530,7 +4698,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>403</v>
@@ -4554,7 +4722,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>407</v>
@@ -4566,7 +4734,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>409</v>
@@ -4578,7 +4746,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>411</v>
@@ -4590,7 +4758,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>413</v>
@@ -4662,7 +4830,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>425</v>
@@ -4674,7 +4842,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>427</v>
@@ -4686,7 +4854,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>429</v>
@@ -4698,7 +4866,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>431</v>
@@ -4710,7 +4878,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>433</v>
@@ -4722,7 +4890,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>435</v>
@@ -4734,7 +4902,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>437</v>
@@ -4746,7 +4914,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>439</v>
@@ -4770,7 +4938,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>443</v>
@@ -4782,7 +4950,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>445</v>
@@ -4806,7 +4974,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>449</v>
@@ -4818,7 +4986,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>451</v>
@@ -4830,7 +4998,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>453</v>
@@ -4842,7 +5010,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>455</v>
@@ -4866,7 +5034,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>459</v>
@@ -4890,7 +5058,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>463</v>
@@ -4902,7 +5070,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>465</v>
@@ -4962,7 +5130,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>475</v>
@@ -4974,7 +5142,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>477</v>
@@ -4986,7 +5154,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>479</v>
@@ -4998,7 +5166,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>481</v>
@@ -5022,7 +5190,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>485</v>
@@ -5058,7 +5226,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>491</v>
@@ -5070,7 +5238,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>493</v>
@@ -5082,7 +5250,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>495</v>
@@ -5094,7 +5262,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>497</v>
@@ -5106,7 +5274,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>499</v>
@@ -5118,7 +5286,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>501</v>
@@ -5178,7 +5346,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>511</v>
@@ -5190,7 +5358,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>513</v>
@@ -5202,7 +5370,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>515</v>
@@ -5226,7 +5394,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>519</v>
@@ -5238,7 +5406,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>521</v>
@@ -5250,7 +5418,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>523</v>
@@ -5262,7 +5430,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>525</v>
@@ -5274,7 +5442,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>527</v>
@@ -5286,7 +5454,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>529</v>
@@ -5298,7 +5466,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>531</v>
@@ -5310,7 +5478,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>533</v>
@@ -5334,7 +5502,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>537</v>
@@ -5346,7 +5514,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>539</v>
@@ -5358,7 +5526,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>541</v>
@@ -5430,7 +5598,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>553</v>
@@ -5442,7 +5610,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>555</v>
@@ -5454,7 +5622,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>557</v>
@@ -5514,7 +5682,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>567</v>
@@ -5526,7 +5694,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>569</v>
@@ -5538,7 +5706,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>571</v>
@@ -5550,7 +5718,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>573</v>
@@ -5562,7 +5730,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>575</v>
@@ -5574,7 +5742,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>577</v>
@@ -5586,7 +5754,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>579</v>
@@ -5598,7 +5766,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>581</v>
@@ -5610,7 +5778,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>583</v>
@@ -5622,7 +5790,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>585</v>
@@ -5646,7 +5814,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>589</v>
@@ -5658,7 +5826,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>591</v>
@@ -5670,7 +5838,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>593</v>
@@ -5682,7 +5850,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>595</v>
@@ -5694,7 +5862,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>597</v>
@@ -5706,7 +5874,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>599</v>
@@ -5718,7 +5886,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>601</v>
@@ -5742,7 +5910,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>605</v>
@@ -5754,7 +5922,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>607</v>
@@ -5766,7 +5934,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>609</v>
@@ -5778,7 +5946,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>611</v>
@@ -5802,7 +5970,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>615</v>
@@ -5814,7 +5982,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>617</v>
@@ -5826,7 +5994,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>619</v>
@@ -5838,7 +6006,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>621</v>
@@ -5850,7 +6018,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>623</v>
@@ -5862,7 +6030,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>625</v>
@@ -5898,7 +6066,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>631</v>
@@ -5958,7 +6126,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>641</v>
@@ -5970,7 +6138,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>643</v>
@@ -5982,7 +6150,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>645</v>
@@ -5994,7 +6162,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>647</v>
@@ -6018,7 +6186,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>651</v>
@@ -6030,7 +6198,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>653</v>
@@ -6042,7 +6210,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>655</v>
@@ -6054,7 +6222,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>657</v>
@@ -6066,7 +6234,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>659</v>
@@ -6078,7 +6246,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>661</v>
@@ -6090,7 +6258,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>663</v>
@@ -6102,7 +6270,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>665</v>
@@ -6114,7 +6282,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>667</v>
@@ -6126,7 +6294,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>669</v>
@@ -6138,7 +6306,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>671</v>
@@ -6150,7 +6318,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>673</v>
@@ -6162,7 +6330,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>675</v>
@@ -6174,7 +6342,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>677</v>
@@ -6183,6 +6351,342 @@
         <v>678</v>
       </c>
       <c r="D318" s="2"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B319" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C319" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="D319" s="2"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B320" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C320" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="D320" s="2"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B321" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C321" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="D321" s="2"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B322" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C322" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="D322" s="2"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B323" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C323" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="D323" s="2"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B324" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C324" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="D324" s="2"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B325" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C325" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="D325" s="2"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B326" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C326" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="D326" s="2"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B327" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C327" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="D327" s="2"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B328" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C328" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="D328" s="2"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B329" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C329" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="D329" s="2"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B330" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C330" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="D330" s="2"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B331" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C331" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="D331" s="2"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B332" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C332" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="D332" s="2"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B333" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C333" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="D333" s="2"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B334" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C334" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="D334" s="2"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B335" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C335" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="D335" s="2"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B336" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C336" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="D336" s="2"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B337" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="C337" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="D337" s="2"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B338" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C338" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="D338" s="2"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B339" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C339" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="D339" s="2"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B340" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="C340" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="D340" s="2"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B341" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C341" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="D341" s="2"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B342" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C342" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="D342" s="2"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B343" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C343" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="D343" s="2"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B344" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C344" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="D344" s="2"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B345" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C345" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="D345" s="2"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B346" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C346" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="D346" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.176.2.4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="737">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -2194,6 +2194,12 @@
   </si>
   <si>
     <t>Hjemmeblodtryksmåling udført af patienten</t>
+  </si>
+  <si>
+    <t>ZZ5048</t>
+  </si>
+  <si>
+    <t>Hoehn og Yahr scale (HY)</t>
   </si>
   <si>
     <t>ZZ7011</t>
@@ -2531,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D347"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6666,7 +6672,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>731</v>
@@ -6687,6 +6693,18 @@
         <v>734</v>
       </c>
       <c r="D346" s="2"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B347" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C347" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="D347" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
